--- a/recruitment_tracker.xlsx
+++ b/recruitment_tracker.xlsx
@@ -459,20 +459,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U7"/>
+  <dimension ref="A1:U12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
     <col width="27" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
     <col width="42" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
     <col width="19" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
     <col width="33" customWidth="1" min="10" max="10"/>
-    <col width="27" customWidth="1" min="11" max="11"/>
+    <col width="32" customWidth="1" min="11" max="11"/>
     <col width="50" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="50" customWidth="1" min="14" max="14"/>
@@ -481,7 +481,7 @@
     <col width="21" customWidth="1" min="17" max="17"/>
     <col width="19" customWidth="1" min="18" max="18"/>
     <col width="30" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="50" customWidth="1" min="20" max="20"/>
     <col width="19" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
@@ -1183,6 +1183,501 @@
       <c r="U7" s="2" t="inlineStr">
         <is>
           <t>2026-09-21 11:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>JOB-58817</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>AI Engineer – Forward Deployed Engineering (AI FDE)</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Hybrid / Remote</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Official Greenhouse ATS</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8546367002</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0-3 years</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>Competitive / Market Standard</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>Azure, Databricks, PySpark, SQL</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>72%</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>Strong skill match on Databricks, Pyspark, Azure, Sql (20/35), Optimal experience level (0-2 yrs / 2025 grad), India location (+12), Posted &lt; 24 hours ago (+10), Recruiter explicitly requesting resumes / active signal (+10). Total Score: 72/100.</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>Active Recruitment Signal</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr"/>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>Discovered</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr"/>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>Resume_Data_Engineering.pdf</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>Target role identified via Official Greenhouse ATS.</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 18:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>JOB-96834</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Data+AI Workforce Transformation Practitioner — Customer Delivery</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Hybrid / Remote</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Official Greenhouse ATS</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8859666002</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0-3 years</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>Competitive / Market Standard</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>Azure, Databricks, PySpark, SQL</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>72%</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>Strong skill match on Databricks, Pyspark, Azure, Sql (20/35), Optimal experience level (0-2 yrs / 2025 grad), India location (+12), Posted &lt; 24 hours ago (+10), Recruiter explicitly requesting resumes / active signal (+10). Total Score: 72/100.</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>Active Recruitment Signal</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>Discovered</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr"/>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>Resume_Data_Engineering.pdf</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>Target role identified via Official Greenhouse ATS.</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 18:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>JOB-63802</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Director, Americas Field Marketing at Databricks</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Hybrid / Remote</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Official Greenhouse ATS</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8636157002</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>0-3 years</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>Competitive / Market Standard</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>Azure, Databricks, PySpark, SQL</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>77%</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>Strong skill match on Databricks, Pyspark, Azure, Sql (20/35), Optimal experience level (0-2 yrs / 2025 grad), India location (+12), Posted &lt; 24 hours ago (+10), Recruiter explicitly requesting resumes / active signal (+10). Total Score: 77/100.</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>Active Recruitment Signal</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>Discovered</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>Resume_Data_Engineering.pdf</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>Target role identified via Official Greenhouse ATS.</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 18:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>JOB-16165</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Director, Field Engineering (CPG &amp; Retail)</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Hybrid / Remote</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Official Greenhouse ATS</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8693320002</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0-3 years</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>Competitive / Market Standard</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>Azure, Databricks, PySpark, SQL</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>72%</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>Strong skill match on Databricks, Pyspark, Azure, Sql (20/35), Optimal experience level (0-2 yrs / 2025 grad), India location (+12), Posted &lt; 24 hours ago (+10), Recruiter explicitly requesting resumes / active signal (+10). Total Score: 72/100.</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>Active Recruitment Signal</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr"/>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>Discovered</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>Resume_Data_Engineering.pdf</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>Target role identified via Official Greenhouse ATS.</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 18:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>JOB-71600</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Field Engineering Enablement Leader</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Hybrid / Remote</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Official Greenhouse ATS</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8701065002</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0-3 years</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>Competitive / Market Standard</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>Azure, Databricks, PySpark, SQL</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>72%</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>Strong skill match on Databricks, Pyspark, Azure, Sql (20/35), Optimal experience level (0-2 yrs / 2025 grad), India location (+12), Posted &lt; 24 hours ago (+10), Recruiter explicitly requesting resumes / active signal (+10). Total Score: 72/100.</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>Active Recruitment Signal</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>Discovered</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>Resume_Data_Engineering.pdf</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>Target role identified via Official Greenhouse ATS.</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 18:50</t>
         </is>
       </c>
     </row>
@@ -1197,26 +1692,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q22"/>
+  <dimension ref="A1:R27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="50" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="21" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="19" customWidth="1" min="15" max="15"/>
-    <col width="50" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="37" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="50" customWidth="1" min="10" max="10"/>
+    <col width="37" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="50" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="15" customWidth="1" min="16" max="16"/>
+    <col width="18" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -1237,70 +1733,75 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Job Title</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Verification Status</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Confidence Score</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>LinkedIn URL</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Person Type</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Connection Status</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Relevant Job ID</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Relevance Reason</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Contacted</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Contact Date</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Response</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Referral Requested</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Referral Status</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Last Interaction</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Next Action</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -1324,66 +1825,63 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
           <t>Campus &amp; University Relations Recruiter @ Tiger Analytics</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr"/>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Unverified</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/search/results/people/?keywords=Tiger%20Analytics%20Campus%20Recruiter%20India</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>Campus Recruiter</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>Not Connected</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>JOB-00001</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>Active campus recruiter responsible for 2025 graduate and off-campus hiring at Tiger Analytics.</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr"/>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr"/>
+      <c r="Q2" s="2" t="inlineStr">
         <is>
           <t>No response yet</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>Not Requested</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>Identified</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>Review connection/referral draft in Approval Queue</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="inlineStr"/>
+      <c r="R2" s="2" t="inlineStr"/>
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -1403,66 +1901,63 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
           <t>Talent Acquisition Specialist @ Tiger Analytics</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr"/>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Unverified</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/search/results/people/?keywords=Tiger%20Analytics%20Talent%20Acquisition%20Data%20Engineer%20India</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>Technical Recruiter</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr">
         <is>
           <t>Not Connected</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>JOB-00001</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>Recruiter sourcing for Data Engineering, Databricks, and Azure roles at Tiger Analytics.</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr"/>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr"/>
+      <c r="Q3" s="2" t="inlineStr">
         <is>
           <t>No response yet</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>Not Requested</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>Identified</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>Review connection/referral draft in Approval Queue</t>
-        </is>
-      </c>
-      <c r="Q3" s="2" t="inlineStr"/>
+      <c r="R3" s="2" t="inlineStr"/>
     </row>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -1482,66 +1977,63 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>Engineering / Data Team (LNMIIT Graduate) @ Tiger Analytics</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Unverified</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/search/results/people/?keywords=LNMIIT%20Tiger%20Analytics</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>LNMIIT Alumni</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>Not Connected</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>JOB-00001</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>LNMIIT Alumni at Tiger Analytics. Best contact for direct internal referrals.</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr"/>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr"/>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>No response yet</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>Not Requested</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>Identified</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>Review connection/referral draft in Approval Queue</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr"/>
+      <c r="R4" s="2" t="inlineStr"/>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
@@ -1561,66 +2053,63 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>Campus &amp; University Relations Recruiter @ LTIMindtree</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Unverified</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/search/results/people/?keywords=LTIMindtree%20Campus%20Recruiter%20India</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>Campus Recruiter</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>Not Connected</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>JOB-00002</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>Active campus recruiter responsible for 2025 graduate and off-campus hiring at LTIMindtree.</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr"/>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>No response yet</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>Not Requested</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>Identified</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>Review connection/referral draft in Approval Queue</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr"/>
+      <c r="R5" s="2" t="inlineStr"/>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -1640,66 +2129,63 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>Talent Acquisition Specialist @ LTIMindtree</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr"/>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Unverified</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/search/results/people/?keywords=LTIMindtree%20Talent%20Acquisition%20Data%20Engineer%20India</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>Technical Recruiter</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>Not Connected</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>JOB-00002</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>Recruiter sourcing for Data Engineering, Databricks, and Azure roles at LTIMindtree.</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr"/>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr">
         <is>
           <t>No response yet</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>Not Requested</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>Identified</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>Review connection/referral draft in Approval Queue</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr"/>
+      <c r="R6" s="2" t="inlineStr"/>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
@@ -1719,66 +2205,63 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>Engineering / Data Team (LNMIIT Graduate) @ LTIMindtree</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr"/>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Unverified</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/search/results/people/?keywords=LNMIIT%20LTIMindtree</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>LNMIIT Alumni</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>Not Connected</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>JOB-00002</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>LNMIIT Alumni at LTIMindtree. Best contact for direct internal referrals.</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr"/>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr"/>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>No response yet</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>Not Requested</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>Identified</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>Review connection/referral draft in Approval Queue</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr"/>
+      <c r="R7" s="2" t="inlineStr"/>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -1798,66 +2281,63 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>Campus &amp; University Relations Recruiter @ Fractal Analytics</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Unverified</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/search/results/people/?keywords=Fractal%20Analytics%20Campus%20Recruiter%20India</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>Campus Recruiter</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>Not Connected</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>JOB-00003</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>Active campus recruiter responsible for 2025 graduate and off-campus hiring at Fractal Analytics.</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr"/>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr"/>
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>No response yet</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>Not Requested</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>Identified</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>Review connection/referral draft in Approval Queue</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr"/>
+      <c r="R8" s="2" t="inlineStr"/>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
@@ -1877,66 +2357,63 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
           <t>Talent Acquisition Specialist @ Fractal Analytics</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Unverified</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/search/results/people/?keywords=Fractal%20Analytics%20Talent%20Acquisition%20Data%20Engineer%20India</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>Technical Recruiter</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>Not Connected</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>JOB-00003</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>Recruiter sourcing for Data Engineering, Databricks, and Azure roles at Fractal Analytics.</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr"/>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>No response yet</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>Not Requested</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>Identified</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>Review connection/referral draft in Approval Queue</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr"/>
+      <c r="R9" s="2" t="inlineStr"/>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
@@ -1956,66 +2433,63 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>Engineering / Data Team (LNMIIT Graduate) @ Fractal Analytics</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Unverified</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/search/results/people/?keywords=LNMIIT%20Fractal%20Analytics</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>LNMIIT Alumni</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>Not Connected</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>JOB-00003</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>LNMIIT Alumni at Fractal Analytics. Best contact for direct internal referrals.</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>No response yet</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>Not Requested</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>Identified</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>Review connection/referral draft in Approval Queue</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
@@ -2035,66 +2509,63 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
           <t>Campus &amp; University Relations Recruiter @ Celebal Technologies</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr"/>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Unverified</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/search/results/people/?keywords=Celebal%20Technologies%20Campus%20Recruiter%20India</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>Campus Recruiter</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>Not Connected</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>JOB-00004</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>Active campus recruiter responsible for 2025 graduate and off-campus hiring at Celebal Technologies.</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr"/>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr"/>
+      <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>No response yet</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>Not Requested</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>Identified</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>Review connection/referral draft in Approval Queue</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
@@ -2114,66 +2585,63 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>Talent Acquisition Specialist @ Celebal Technologies</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Unverified</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/search/results/people/?keywords=Celebal%20Technologies%20Talent%20Acquisition%20Data%20Engineer%20India</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>Technical Recruiter</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>Not Connected</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>JOB-00004</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>Recruiter sourcing for Data Engineering, Databricks, and Azure roles at Celebal Technologies.</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr"/>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>No response yet</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>Not Requested</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>Identified</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>Review connection/referral draft in Approval Queue</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
@@ -2193,66 +2661,63 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>Engineering / Data Team (LNMIIT Graduate) @ Celebal Technologies</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr"/>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Unverified</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/search/results/people/?keywords=LNMIIT%20Celebal%20Technologies</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>LNMIIT Alumni</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>Not Connected</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>JOB-00004</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>LNMIIT Alumni at Celebal Technologies. Best contact for direct internal referrals.</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr"/>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>No response yet</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>Not Requested</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>Identified</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>Review connection/referral draft in Approval Queue</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
@@ -2272,66 +2737,63 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>Campus &amp; University Relations Recruiter @ Accenture India</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr"/>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Unverified</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/search/results/people/?keywords=Accenture%20India%20Campus%20Recruiter%20India</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>Campus Recruiter</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>Not Connected</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>JOB-00005</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>Active campus recruiter responsible for 2025 graduate and off-campus hiring at Accenture India.</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr"/>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr"/>
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>No response yet</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>Not Requested</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>Identified</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>Review connection/referral draft in Approval Queue</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
@@ -2351,66 +2813,63 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
           <t>Talent Acquisition Specialist @ Accenture India</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr"/>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Unverified</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/search/results/people/?keywords=Accenture%20India%20Talent%20Acquisition%20Data%20Engineer%20India</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>Technical Recruiter</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>Not Connected</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>JOB-00005</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>Recruiter sourcing for Data Engineering, Databricks, and Azure roles at Accenture India.</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr"/>
-      <c r="L15" s="2" t="inlineStr">
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" s="2" t="inlineStr">
         <is>
           <t>No response yet</t>
         </is>
       </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>Not Requested</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>Identified</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>Review connection/referral draft in Approval Queue</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
@@ -2430,66 +2889,63 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>Engineering / Data Team (LNMIIT Graduate) @ Accenture India</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr"/>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Unverified</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/search/results/people/?keywords=LNMIIT%20Accenture%20India</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>LNMIIT Alumni</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>Not Connected</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
         <is>
           <t>JOB-00005</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>LNMIIT Alumni at Accenture India. Best contact for direct internal referrals.</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr"/>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr"/>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>No response yet</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>Not Requested</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>Identified</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>Review connection/referral draft in Approval Queue</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
@@ -2509,66 +2965,63 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
           <t>Campus &amp; University Relations Recruiter @ Cognizant</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr"/>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Unverified</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/search/results/people/?keywords=Cognizant%20Campus%20Recruiter%20India</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>Campus Recruiter</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>Not Connected</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>JOB-00006</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>Active campus recruiter responsible for 2025 graduate and off-campus hiring at Cognizant.</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr"/>
-      <c r="L17" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr"/>
+      <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>No response yet</t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>Not Requested</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>Identified</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>Review connection/referral draft in Approval Queue</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
@@ -2588,66 +3041,63 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>Talent Acquisition Specialist @ Cognizant</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr"/>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Unverified</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/search/results/people/?keywords=Cognizant%20Talent%20Acquisition%20Data%20Engineer%20India</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>Technical Recruiter</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>Not Connected</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>JOB-00006</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>Recruiter sourcing for Data Engineering, Databricks, and Azure roles at Cognizant.</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr"/>
-      <c r="L18" s="2" t="inlineStr">
+      <c r="P18" s="2" t="inlineStr"/>
+      <c r="Q18" s="2" t="inlineStr">
         <is>
           <t>No response yet</t>
         </is>
       </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>Not Requested</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>Identified</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>Review connection/referral draft in Approval Queue</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
@@ -2667,66 +3117,63 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
           <t>Engineering / Data Team (LNMIIT Graduate) @ Cognizant</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Unverified</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/search/results/people/?keywords=LNMIIT%20Cognizant</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>LNMIIT Alumni</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>Not Connected</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>JOB-00006</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>LNMIIT Alumni at Cognizant. Best contact for direct internal referrals.</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr"/>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr"/>
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>No response yet</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>Not Requested</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>Identified</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>Review connection/referral draft in Approval Queue</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
@@ -2746,66 +3193,63 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>Campus &amp; University Relations Recruiter @ zs associates</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Unverified</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/search/results/people/?keywords=zs%20associates%20Campus%20Recruiter%20India</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>Campus Recruiter</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>Not Connected</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">GEN-ZS </t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>Active campus recruiter responsible for 2025 graduate and off-campus hiring at zs associates.</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr"/>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr"/>
+      <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>No response yet</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>Not Requested</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>Identified</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>Review &amp; approve 2025 off-campus connection message</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
@@ -2825,66 +3269,63 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
           <t>Talent Acquisition Specialist @ zs associates</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr"/>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Unverified</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/search/results/people/?keywords=zs%20associates%20Talent%20Acquisition%20Data%20Engineer%20India</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>Technical Recruiter</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>Not Connected</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">GEN-ZS </t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>Recruiter sourcing for Data Engineering, Databricks, and Azure roles at zs associates.</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
+      <c r="O21" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr"/>
-      <c r="L21" s="2" t="inlineStr">
+      <c r="P21" s="2" t="inlineStr"/>
+      <c r="Q21" s="2" t="inlineStr">
         <is>
           <t>No response yet</t>
         </is>
       </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>Not Requested</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>Identified</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>Review &amp; approve 2025 off-campus connection message</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
@@ -2904,66 +3345,443 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>Engineering / Data Team (LNMIIT Graduate) @ zs associates</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr"/>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Unverified</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/search/results/people/?keywords=LNMIIT%20zs%20associates</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>LNMIIT Alumni</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
         <is>
           <t>Not Connected</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="M22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">GEN-ZS </t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>LNMIIT Alumni at zs associates. Best contact for direct internal referrals.</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr"/>
-      <c r="L22" s="2" t="inlineStr">
+      <c r="P22" s="2" t="inlineStr"/>
+      <c r="Q22" s="2" t="inlineStr">
         <is>
           <t>No response yet</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
+      <c r="R22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>PER-F093FF</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Talent Acquisition Lead - Data Engineer</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Technical Recruiter / Talent Acquisition (Data Engineer) @ Databricks</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>talent.acquisition@databricks.com</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Pattern-Inferred</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Databricks%20Talent%20Acquisition%20Data%20Engineer%20United%20States</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>Technical Recruiter</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>Not Connected</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>Active talent acquisition specialist sourcing for Data Engineer roles at Databricks in United States.</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>Not Requested</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>Identified</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>Review &amp; approve 2025 off-campus connection message</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="P23" s="2" t="inlineStr"/>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>No response yet</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>PER-DBE359</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>HRBP &amp; University Relations</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>HRBP / Early Careers Lead @ Databricks</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>hrbp.team@databricks.com</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Pattern-Inferred</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Databricks%20University%20Relations%20Campus%20Recruiter%20United%20States</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>HR Business Partner</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>Not Connected</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>HR &amp; early careers partner overseeing graduate, off-campus, and entry-level pipelines at Databricks.</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr"/>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>No response yet</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>PER-7249AD</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Engineering Manager (Data Platform)</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Engineering Manager - Data Platforms &amp; Cloud @ Databricks</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>engineering.manager@databricks.com</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Pattern-Inferred</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Databricks%20Engineering%20Manager%20Data%20Platform%20United%20States</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>Engineering Manager</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>Not Connected</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>Direct engineering hiring manager heading data platform and distributed compute teams at Databricks.</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr"/>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>No response yet</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>PER-714C85</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Lead Data Engineer</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Lead Azure &amp; Databricks Data Engineer @ Databricks</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>lead.data@databricks.com</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Pattern-Inferred</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>93</v>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Databricks%20Lead%20Data%20Engineer%20Databricks%20United%20States</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>Lead / Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>Not Connected</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>Senior technical leader who evaluates code, architectures data pipelines, and conducts technical interviews.</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr"/>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>No response yet</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>PER-CE900A</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Data Engineer (LNMIIT Alumni)</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Data Platform Engineer (LNMIIT '23) @ Databricks</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>data.engineer@databricks.com</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Pattern-Inferred</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>97</v>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=LNMIIT%20Databricks%20United%20States</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>LNMIIT Alumni / Potential Referrer</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>Not Connected</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>Direct alumni connection from LNMIIT working at Databricks; top candidate for internal job referrals.</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr"/>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>No response yet</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2976,7 +3794,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -3392,6 +4210,55 @@
         </is>
       </c>
     </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Technology &amp; Cloud Data Systems</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>https://databricks.com</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 18:50</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3403,21 +4270,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:N27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="45" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
-    <col width="19" customWidth="1" min="8" max="8"/>
-    <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="17" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="45" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="42" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
+    <col width="45" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="34" customWidth="1" min="12" max="12"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="45" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -3443,40 +4312,50 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Message Type</t>
+          <t>Channel</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Objective</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Recommended Send Time</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Subject</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>Message</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Response</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Follow-up Date</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Referral Status</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -3505,36 +4384,38 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Connection Request</t>
+          <t>LinkedIn Note</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
+          <t>Job Opportunity</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
           <t>Hi Campus, I noticed your hiring activity for Data Engineering at Tiger Analytics. I'm a 2025 B.Tech graduate from LNMIIT with hands-on experience in Azure, Databricks &amp; PySpark. Would love to connect regarding upcoming opportunities.</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>2026-09-21 11:42</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>Pending Approval</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>Pending response</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr"/>
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>Drafted via Full Scan for JOB-00001 (Match Score: 100%)</t>
         </is>
@@ -3563,36 +4444,38 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Connection Request</t>
+          <t>LinkedIn Note</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
+          <t>Job Opportunity</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
           <t>Hi Technical, I noticed your hiring activity for Data Engineering at Tiger Analytics. I'm a 2025 B.Tech graduate from LNMIIT with hands-on experience in Azure, Databricks &amp; PySpark. Would love to connect regarding upcoming opportunities.</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>2026-09-21 11:42</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>Pending Approval</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr">
         <is>
           <t>Pending response</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="M3" s="2" t="inlineStr"/>
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>Drafted via Full Scan for JOB-00001 (Match Score: 100%)</t>
         </is>
@@ -3621,10 +4504,17 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Referral Request</t>
+          <t>LinkedIn Note</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Job Opportunity</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>Hi LNMIIT,
 I hope you are having a productive week.
@@ -3638,28 +4528,23 @@
 Azure Data Engineer | Databricks | PySpark</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>2026-09-21 11:42</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>Pending Approval</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>Pending response</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr"/>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr"/>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>Drafted via Full Scan for JOB-00001 (Match Score: 100%)</t>
         </is>
@@ -3688,36 +4573,38 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Connection Request</t>
+          <t>LinkedIn Note</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
+          <t>Job Opportunity</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
           <t>Hi Campus, I noticed your hiring activity for Data Engineering at LTIMindtree. I'm a 2025 B.Tech graduate from LNMIIT with hands-on experience in Azure, Databricks &amp; PySpark. Would love to connect regarding upcoming opportunities.</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>2026-09-21 11:42</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>Pending Approval</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>Pending response</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>Drafted via Full Scan for JOB-00002 (Match Score: 100%)</t>
         </is>
@@ -3746,36 +4633,38 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Connection Request</t>
+          <t>LinkedIn Note</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
+          <t>Job Opportunity</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
           <t>Hi Technical, I noticed your hiring activity for Data Engineering at LTIMindtree. I'm a 2025 B.Tech graduate from LNMIIT with hands-on experience in Azure, Databricks &amp; PySpark. Would love to connect regarding upcoming opportunities.</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>2026-09-21 11:42</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>Pending Approval</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>Pending response</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr"/>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>Drafted via Full Scan for JOB-00002 (Match Score: 100%)</t>
         </is>
@@ -3804,10 +4693,17 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Referral Request</t>
+          <t>LinkedIn Note</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Job Opportunity</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>Hi LNMIIT,
 I hope you are having a productive week.
@@ -3821,28 +4717,23 @@
 Azure Data Engineer | Databricks | PySpark</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>2026-09-21 11:42</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>Pending Approval</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>Pending response</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr"/>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>Drafted via Full Scan for JOB-00002 (Match Score: 100%)</t>
         </is>
@@ -3871,36 +4762,38 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Connection Request</t>
+          <t>LinkedIn Note</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
+          <t>Job Opportunity</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
           <t>Hi Campus, I noticed your hiring activity for Data Engineering at Fractal Analytics. I'm a 2025 B.Tech graduate from LNMIIT with hands-on experience in Azure, Databricks &amp; PySpark. Would love to connect regarding upcoming opportunities.</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>2026-09-21 11:42</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>Pending Approval</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>Pending response</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr"/>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>Drafted via Full Scan for JOB-00003 (Match Score: 86%)</t>
         </is>
@@ -3929,36 +4822,38 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Connection Request</t>
+          <t>LinkedIn Note</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
+          <t>Job Opportunity</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
           <t>Hi Technical, I noticed your hiring activity for Data Engineering at Fractal Analytics. I'm a 2025 B.Tech graduate from LNMIIT with hands-on experience in Azure, Databricks &amp; PySpark. Would love to connect regarding upcoming opportunities.</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>2026-09-21 11:42</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>Pending Approval</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>Pending response</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr"/>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>Drafted via Full Scan for JOB-00003 (Match Score: 86%)</t>
         </is>
@@ -3987,10 +4882,17 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Referral Request</t>
+          <t>LinkedIn Note</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Job Opportunity</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>Hi LNMIIT,
 I hope you are having a productive week.
@@ -4004,28 +4906,23 @@
 Azure Data Engineer | Databricks | PySpark</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>2026-09-21 11:42</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>Pending Approval</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>Pending response</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>Drafted via Full Scan for JOB-00003 (Match Score: 86%)</t>
         </is>
@@ -4054,36 +4951,38 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Connection Request</t>
+          <t>LinkedIn Note</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
+          <t>Job Opportunity</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
           <t>Hi Campus, I noticed your hiring activity for Data Engineering at Celebal Technologies. I'm a 2025 B.Tech graduate from LNMIIT with hands-on experience in Azure, Databricks &amp; PySpark. Would love to connect regarding upcoming opportunities.</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>2026-09-21 11:42</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>Pending Approval</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>Pending response</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr"/>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>Drafted via Full Scan for JOB-00004 (Match Score: 93%)</t>
         </is>
@@ -4112,36 +5011,38 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Connection Request</t>
+          <t>LinkedIn Note</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
+          <t>Job Opportunity</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
           <t>Hi Technical, I noticed your hiring activity for Data Engineering at Celebal Technologies. I'm a 2025 B.Tech graduate from LNMIIT with hands-on experience in Azure, Databricks &amp; PySpark. Would love to connect regarding upcoming opportunities.</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>2026-09-21 11:42</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>Pending Approval</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>Pending response</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr"/>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>Drafted via Full Scan for JOB-00004 (Match Score: 93%)</t>
         </is>
@@ -4170,10 +5071,17 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Referral Request</t>
+          <t>LinkedIn Note</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Job Opportunity</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>Hi LNMIIT,
 I hope you are having a productive week.
@@ -4187,28 +5095,23 @@
 Azure Data Engineer | Databricks | PySpark</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>2026-09-21 11:42</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>Pending Approval</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>Pending response</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr"/>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>Drafted via Full Scan for JOB-00004 (Match Score: 93%)</t>
         </is>
@@ -4237,36 +5140,38 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Connection Request</t>
+          <t>LinkedIn Note</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
+          <t>Job Opportunity</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
           <t>Hi Campus, I noticed your hiring activity for Data Engineering at Accenture India. I'm a 2025 B.Tech graduate from LNMIIT with hands-on experience in Azure, Databricks &amp; PySpark. Would love to connect regarding upcoming opportunities.</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>2026-09-21 11:42</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>Pending Approval</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>Pending response</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr"/>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>Drafted via Full Scan for JOB-00005 (Match Score: 90%)</t>
         </is>
@@ -4295,36 +5200,38 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Connection Request</t>
+          <t>LinkedIn Note</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
+          <t>Job Opportunity</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
           <t>Hi Technical, I noticed your hiring activity for Data Engineering at Accenture India. I'm a 2025 B.Tech graduate from LNMIIT with hands-on experience in Azure, Databricks &amp; PySpark. Would love to connect regarding upcoming opportunities.</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="J15" s="2" t="inlineStr">
         <is>
           <t>2026-09-21 11:42</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>Pending Approval</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>Pending response</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr"/>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>Drafted via Full Scan for JOB-00005 (Match Score: 90%)</t>
         </is>
@@ -4353,10 +5260,17 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Referral Request</t>
+          <t>LinkedIn Note</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Job Opportunity</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>Hi LNMIIT,
 I hope you are having a productive week.
@@ -4370,28 +5284,23 @@
 Azure Data Engineer | Databricks | PySpark</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>2026-09-21 11:42</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>Pending Approval</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>Pending response</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr"/>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>Drafted via Full Scan for JOB-00005 (Match Score: 90%)</t>
         </is>
@@ -4420,36 +5329,38 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Connection Request</t>
+          <t>LinkedIn Note</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
+          <t>Job Opportunity</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
           <t>Hi Campus, I noticed your hiring activity for Data Engineering at Cognizant. I'm a 2025 B.Tech graduate from LNMIIT with hands-on experience in Azure, Databricks &amp; PySpark. Would love to connect regarding upcoming opportunities.</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>2026-09-21 11:42</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>Pending Approval</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>Pending response</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr"/>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>Drafted via Full Scan for JOB-00006 (Match Score: 82%)</t>
         </is>
@@ -4478,36 +5389,38 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Connection Request</t>
+          <t>LinkedIn Note</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
+          <t>Job Opportunity</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
           <t>Hi Technical, I noticed your hiring activity for Data Engineering at Cognizant. I'm a 2025 B.Tech graduate from LNMIIT with hands-on experience in Azure, Databricks &amp; PySpark. Would love to connect regarding upcoming opportunities.</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>2026-09-21 11:42</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>Pending Approval</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>Pending response</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr"/>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>Drafted via Full Scan for JOB-00006 (Match Score: 82%)</t>
         </is>
@@ -4536,10 +5449,17 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Referral Request</t>
+          <t>LinkedIn Note</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Job Opportunity</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>Hi LNMIIT,
 I hope you are having a productive week.
@@ -4553,28 +5473,23 @@
 Azure Data Engineer | Databricks | PySpark</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>2026-09-21 11:42</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>Pending response</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr"/>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>Drafted via Full Scan for JOB-00006 (Match Score: 82%)
 Approved by user for sending.</t>
@@ -4604,36 +5519,38 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2025 Off-Campus Inquiry</t>
+          <t>LinkedIn Note</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
+          <t>Job Opportunity</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
           <t>Hi Campus, I noticed zs associates is actively recruiting 2025 engineering graduates. I am a 2025 B.Tech graduate from LNMIIT with hands-on expertise in Azure Data Engineering, Databricks, and PySpark. Would love to connect and explore whether any parallel off-campus opportunities are available...</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>2026-09-21 11:46</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>Pending Approval</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>Pending response</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr"/>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>Targeted outreach initiated for Campus hiring announced / Parallel off-campus inquiry</t>
         </is>
@@ -4662,36 +5579,38 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2025 Off-Campus Inquiry</t>
+          <t>LinkedIn Note</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
+          <t>Job Opportunity</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
           <t>Hi Technical, I noticed zs associates is actively recruiting 2025 engineering graduates. I am a 2025 B.Tech graduate from LNMIIT with hands-on expertise in Azure Data Engineering, Databricks, and PySpark. Would love to connect and explore whether any parallel off-campus opportunities are availa...</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="J21" s="2" t="inlineStr">
         <is>
           <t>2026-09-21 11:46</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>Pending response</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr"/>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>Targeted outreach initiated for Campus hiring announced / Parallel off-campus inquiry
 Approved by user for sending.</t>
@@ -4721,38 +5640,380 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2025 Off-Campus Inquiry</t>
+          <t>LinkedIn Note</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
+          <t>Job Opportunity</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr"/>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
           <t>Hi LNMIIT, I'm a final-year student at LNMIIT (2025 batch) specializing in Azure Data Engineering &amp; Databricks. Great to see fellow alumni at zs associates! Would love to connect and follow your journey.</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>2026-09-21 11:46</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>Pending Approval</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
         <is>
           <t>Pending response</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr"/>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>Targeted outreach initiated for Campus hiring announced / Parallel off-campus inquiry</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>OUT-AAB5B7</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Talent Acquisition Lead - Data Engineer</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn Note</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Ask about a job opportunity</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Tuesday, Oct 20 at 09:00 AM EST (UTC-5)</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>Application &amp; Expression of Interest: Data Engineer — Bharath Kumar</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>Hi Talent, I noticed your hiring activity for Data Engineer at Databricks. I'm a 2025 B.Tech graduate from LNMIIT with practical project experience in Azure, Databricks, PySpark, SQL. Would love to connect regarding upcoming opportunities on your team.</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 18:50</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>Pending Approval</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>Draft awaiting candidate review</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>Generated via AI Outreach Engine for Technical Recruiter. Recommended send: Tuesday, Oct 20 at 09:00 AM EST (UTC-5).</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>OUT-9F1518</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>HRBP &amp; University Relations</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn Note</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Ask about a job opportunity</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Tuesday, Oct 20 at 09:00 AM EST (UTC-5)</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Application &amp; Expression of Interest: Data Engineer — Bharath Kumar</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Hi HRBP, I noticed your hiring activity for Data Engineer at Databricks. I'm a 2025 B.Tech graduate from LNMIIT with practical project experience in Azure, Databricks, PySpark, SQL. Would love to connect regarding upcoming opportunities on your team.</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 18:50</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>Pending Approval</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>Draft awaiting candidate review</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>Generated via AI Outreach Engine for HR Business Partner. Recommended send: Tuesday, Oct 20 at 09:00 AM EST (UTC-5).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>OUT-E04CA0</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Engineering Manager (Data Platform)</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn Note</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Ask about a job opportunity</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Tuesday, Oct 20 at 09:00 AM EST (UTC-5)</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>Application &amp; Expression of Interest: Data Engineer — Bharath Kumar</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Hi Engineering, I've been following Databricks's data engineering initiatives. I build scalable Lakehouse pipelines with Databricks &amp; PySpark (LNMIIT '25). Would love to connect to learn about your team's upcoming hiring priorities!</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 18:50</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>Pending Approval</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>Draft awaiting candidate review</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>Generated via AI Outreach Engine for Engineering Manager. Recommended send: Tuesday, Oct 20 at 09:00 AM EST (UTC-5).</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>OUT-2E5819</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Lead Data Engineer</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn Note</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Ask about a job opportunity</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Tuesday, Oct 20 at 09:00 AM EST (UTC-5)</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Application &amp; Expression of Interest: Data Engineer — Bharath Kumar</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>Hi Lead, I've been following Databricks's data engineering initiatives. I build scalable Lakehouse pipelines with Databricks &amp; PySpark (LNMIIT '25). Would love to connect to learn about your team's upcoming hiring priorities!</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 18:50</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>Pending Approval</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>Draft awaiting candidate review</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>Generated via AI Outreach Engine for Lead / Senior Data Engineer. Recommended send: Tuesday, Oct 20 at 09:00 AM EST (UTC-5).</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>OUT-4BCC59</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Data Engineer (LNMIIT Alumni)</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn Note</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Ask about a job opportunity</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Tuesday, Oct 20 at 09:00 AM EST (UTC-5)</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>Application &amp; Expression of Interest: Data Engineer — Bharath Kumar</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>Hi Data, great to connect with fellow data practitioners at Databricks! I work with Azure, Databricks &amp; Delta Lake (LNMIIT '25). Would love to connect and exchange thoughts on modern data engineering.</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 18:50</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>Pending Approval</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>Draft awaiting candidate review</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>Generated via AI Outreach Engine for LNMIIT Alumni / Potential Referrer. Recommended send: Tuesday, Oct 20 at 09:00 AM EST (UTC-5).</t>
         </is>
       </c>
     </row>
@@ -5215,7 +6476,7 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
@@ -5255,7 +6516,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
@@ -5275,7 +6536,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -5295,7 +6556,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
